--- a/Data_Catalogue.xlsx
+++ b/Data_Catalogue.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/klaudiakuba/Desktop/Erasmus/HCU/BYOD/SDG3_Website/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A0F2C6-02BC-BE4C-A995-7BE479582C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9365783-906D-1648-B7A2-D9DF3D89D3AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1000" yWindow="920" windowWidth="28240" windowHeight="17240" xr2:uid="{FF239DC3-10DF-2F4C-B914-7643B2E30554}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
+    <sheet name="Worldwide" sheetId="2" r:id="rId1"/>
+    <sheet name="USA" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="184">
   <si>
     <t>Name </t>
   </si>
@@ -240,6 +241,357 @@
   </si>
   <si>
     <t>there are a lot of people who live in the US, but are not officially registered</t>
+  </si>
+  <si>
+    <t>Data catalogue for Sustainable Development Goal:</t>
+  </si>
+  <si>
+    <t>SDG 3 – Good Health &amp; Well-being</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Global</t>
+  </si>
+  <si>
+    <t>https://www.un.org/sustainabledevelopment/health/</t>
+  </si>
+  <si>
+    <t>Maternal Mortality Ratio</t>
+  </si>
+  <si>
+    <t>WHO / World Bank</t>
+  </si>
+  <si>
+    <t>"https://www.who.int/data/gho "</t>
+  </si>
+  <si>
+    <t>Statistical &amp; public</t>
+  </si>
+  <si>
+    <t>Maternal mortality data regarding pregnancy and birth</t>
+  </si>
+  <si>
+    <t>3.1 – Maternal mortality</t>
+  </si>
+  <si>
+    <t>Compare countries</t>
+  </si>
+  <si>
+    <t>underreporting in countries with weak healthcare systems → uncertainty; different definitions and data collection methods</t>
+  </si>
+  <si>
+    <t>https://data.worldbank.org/indicator/SH.STA.MMRT</t>
+  </si>
+  <si>
+    <t>https://publichealth.jhu.edu/2026/study-higher-maternal-death-rate-in-states-with-abortion-bans</t>
+  </si>
+  <si>
+    <t>news article</t>
+  </si>
+  <si>
+    <t>UNICEF Child Mortality Data</t>
+  </si>
+  <si>
+    <t>UNICEF</t>
+  </si>
+  <si>
+    <t>https://data.unicef.org/topic/child-survival/under-five-mortality/</t>
+  </si>
+  <si>
+    <t>Statistical</t>
+  </si>
+  <si>
+    <t>Neonatal and under-5 mortality</t>
+  </si>
+  <si>
+    <t>3.2 – Child mortality</t>
+  </si>
+  <si>
+    <t>Health system indicator</t>
+  </si>
+  <si>
+    <t>Aggregated</t>
+  </si>
+  <si>
+    <t>Global Health Observatory</t>
+  </si>
+  <si>
+    <t>WHO</t>
+  </si>
+  <si>
+    <t>https://www.who.int/data/gho</t>
+  </si>
+  <si>
+    <t>Global health indicators</t>
+  </si>
+  <si>
+    <t>3.3 – Communicable diseases</t>
+  </si>
+  <si>
+    <t>Disease monitoring</t>
+  </si>
+  <si>
+    <t>Spatial blind spots</t>
+  </si>
+  <si>
+    <t>Global Tuberculosis Report</t>
+  </si>
+  <si>
+    <t>https://www.who.int/teams/global-tuberculosis-programme/tb-reports</t>
+  </si>
+  <si>
+    <t>Tuberculosis cases and deaths</t>
+  </si>
+  <si>
+    <t>3.3 – Tuberculosis</t>
+  </si>
+  <si>
+    <t>Infectious disease tracking</t>
+  </si>
+  <si>
+    <t>Testing gaps</t>
+  </si>
+  <si>
+    <t>World Malaria Report</t>
+  </si>
+  <si>
+    <t>https://www.who.int/teams/global-malaria-programme/reports/world-malaria-report-2024</t>
+  </si>
+  <si>
+    <t>Malaria cases and deaths</t>
+  </si>
+  <si>
+    <t>3.3 – Malaria</t>
+  </si>
+  <si>
+    <t>Global disease burden</t>
+  </si>
+  <si>
+    <t>Regional data gaps</t>
+  </si>
+  <si>
+    <t>Universal Health Coverage</t>
+  </si>
+  <si>
+    <t>https://data360.worldbank.org/en/dataset/WB_UHC</t>
+  </si>
+  <si>
+    <t>Coverage of essential health services</t>
+  </si>
+  <si>
+    <t>3.8 – Health coverage</t>
+  </si>
+  <si>
+    <t>Indicator of access to healthcare</t>
+  </si>
+  <si>
+    <t>Aggregation masks inequalities; different national data bases; difficult interpretation</t>
+  </si>
+  <si>
+    <t>Global Burden of Disease</t>
+  </si>
+  <si>
+    <t>IHME</t>
+  </si>
+  <si>
+    <t>https://www.healthdata.org/research-analysis/gbd</t>
+  </si>
+  <si>
+    <t>Disease burden and mortality</t>
+  </si>
+  <si>
+    <t>3.4 – NCDs</t>
+  </si>
+  <si>
+    <t>Premature mortality</t>
+  </si>
+  <si>
+    <t>Model-based estimates</t>
+  </si>
+  <si>
+    <t>Mental Health Atlas</t>
+  </si>
+  <si>
+    <t>https://www.who.int/teams/mental-health-and-substance-use/data-research/mental-health-atlas</t>
+  </si>
+  <si>
+    <t>Qualitative</t>
+  </si>
+  <si>
+    <t>Mental health systems</t>
+  </si>
+  <si>
+    <t>3.4 – Mental health</t>
+  </si>
+  <si>
+    <t>System comparison</t>
+  </si>
+  <si>
+    <t>Underreporting / stigma</t>
+  </si>
+  <si>
+    <t>UNODC Drug Data</t>
+  </si>
+  <si>
+    <t>UNODC</t>
+  </si>
+  <si>
+    <t>https://www.unodc.org/unodc/en/data-and-analysis/index.html</t>
+  </si>
+  <si>
+    <t>Drug use and treatment data</t>
+  </si>
+  <si>
+    <t>3.5 – Substance abuse</t>
+  </si>
+  <si>
+    <t>Policy relevance</t>
+  </si>
+  <si>
+    <t>Data gaps</t>
+  </si>
+  <si>
+    <t>Road Safety Data</t>
+  </si>
+  <si>
+    <t>https://www.who.int/teams/social-determinants-of-health/safety-and-mobility/road-safety</t>
+  </si>
+  <si>
+    <t>Traffic deaths and injuries</t>
+  </si>
+  <si>
+    <t>3.6 – Road safety</t>
+  </si>
+  <si>
+    <t>Infrastructure safety</t>
+  </si>
+  <si>
+    <t>Estimated</t>
+  </si>
+  <si>
+    <t>UNFPA Data Portal</t>
+  </si>
+  <si>
+    <t>UNFPA</t>
+  </si>
+  <si>
+    <t>https://www.unfpa.org/data</t>
+  </si>
+  <si>
+    <t>Sexual and reproductive health</t>
+  </si>
+  <si>
+    <t>3.7 – Reproductive health</t>
+  </si>
+  <si>
+    <t>Inequality analysis</t>
+  </si>
+  <si>
+    <t>Urban bias</t>
+  </si>
+  <si>
+    <t>UHC Service Coverage Index</t>
+  </si>
+  <si>
+    <t>https://www.who.int/data/gho/data/themes/universal-health-coverage</t>
+  </si>
+  <si>
+    <t>Universal health coverage</t>
+  </si>
+  <si>
+    <t>Global overview</t>
+  </si>
+  <si>
+    <t>Masks local inequality</t>
+  </si>
+  <si>
+    <t>Air Pollution Data</t>
+  </si>
+  <si>
+    <t>https://www.who.int/data/gho/data/themes/air-pollution</t>
+  </si>
+  <si>
+    <t>Geospatial</t>
+  </si>
+  <si>
+    <t>Air pollution exposure</t>
+  </si>
+  <si>
+    <t>3.9 – Pollution</t>
+  </si>
+  <si>
+    <t>Environmental health</t>
+  </si>
+  <si>
+    <t>Uneven coverage</t>
+  </si>
+  <si>
+    <t>https://www.euronews.com/health/2026/03/19/air-pollution-linked-to-greater-health-risks-in-poorer-european-regions-study-finds</t>
+  </si>
+  <si>
+    <t>News article</t>
+  </si>
+  <si>
+    <t>https://aqicn.org/api/</t>
+  </si>
+  <si>
+    <t>API Geospatial Data</t>
+  </si>
+  <si>
+    <t>Health Workforce Data</t>
+  </si>
+  <si>
+    <t>World Bank</t>
+  </si>
+  <si>
+    <t>https://data.worldbank.org/topic/health</t>
+  </si>
+  <si>
+    <t>Doctors, nurses and health spending</t>
+  </si>
+  <si>
+    <t>3.C – Health workforce</t>
+  </si>
+  <si>
+    <t>Capacity indicator</t>
+  </si>
+  <si>
+    <t>National-level only</t>
+  </si>
+  <si>
+    <t>Global HIV &amp; AIDS statistics — Fact sheet</t>
+  </si>
+  <si>
+    <t>https://www.unaids.org/en/resources/fact-sheet</t>
+  </si>
+  <si>
+    <t>How widely spread is HIV in different regions</t>
+  </si>
+  <si>
+    <t>3.3 – Communicable diseases - new HIV-Infections per non-infected persons</t>
+  </si>
+  <si>
+    <t>high (global health risk)</t>
+  </si>
+  <si>
+    <t>"Stigmatisation --&gt; underreporting gaps in data avalibilty regarding vulnerable groups limited comparabilty"</t>
+  </si>
+  <si>
+    <t>https://www.da.org.za/2026/04/da-welcomes-arrival-of-hiv-prevention-medicine-in-south-africa</t>
+  </si>
+  <si>
+    <t>Coverage of treatment inventions</t>
+  </si>
+  <si>
+    <t>combinated index of several health services</t>
+  </si>
+  <si>
+    <t>3.5 - Coverage of treatment inventions</t>
+  </si>
+  <si>
+    <t>"aggregation hides details differences in national data sources difficult interpretation for unqualified people"</t>
   </si>
 </sst>
 </file>
@@ -291,7 +643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -310,6 +662,16 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -665,6 +1027,529 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC2E5BF-3282-534B-98DA-CB30DE800D9F}">
+  <dimension ref="A1:H25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="47.33203125" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="28" style="11" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="32.83203125" customWidth="1"/>
+    <col min="6" max="6" width="27.1640625" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="8" max="8" width="63.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="10"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="12"/>
+    </row>
+    <row r="4" spans="1:8" s="9" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="6" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="C7" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="C20" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="C21" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="H22" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" s="5" customFormat="1" ht="51" x14ac:dyDescent="0.2">
+      <c r="A23" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" s="5" customFormat="1" ht="17" x14ac:dyDescent="0.2">
+      <c r="C24" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="5" customFormat="1" ht="34" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{709465EA-6BBE-784E-94D3-ABDC4D6CB076}">
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
